--- a/model/260508 draft/output/topology_results.xlsx
+++ b/model/260508 draft/output/topology_results.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ts_Scale_Free" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ts_Hierarchical" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ts_Modular" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shock_recovery" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30148,4 +30149,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>recovery_time_mean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>recovery_time_sem</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>peak_jump_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>peak_jump_sem</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.94841487750152</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.371605000000002</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9436470034244132</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Small World</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37.14646685756264</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.578657500000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5637879689347983</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scale Free</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.5197225</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4308479102921643</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hierarchical</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.202949999999998</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4113458190614968</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Modular</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9910550000000008</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4343869161962634</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>